--- a/product_upload/packages/21/file.xlsx
+++ b/product_upload/packages/21/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -852,6 +857,11 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>INSULATARD</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-56E9A41A0281</t>
         </is>
       </c>
@@ -875,7 +885,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1046,6 +1056,11 @@
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>INFLUVAC VACCINE</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-B801A7D8AEA3</t>
         </is>
       </c>
@@ -1069,7 +1084,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1236,6 +1251,11 @@
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>INTELENCE 100 MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-D61A20DD140C</t>
         </is>
       </c>
@@ -1259,7 +1279,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1426,6 +1446,11 @@
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>INVEGA 6MG EXTENDED- RELEASE TABLETS</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-0EA25E460F71</t>
         </is>
       </c>
@@ -1449,7 +1474,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1616,6 +1641,11 @@
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>INVEGA 3MG EXTENDED- RELEASE TABLETS</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-FBE7BD17B596</t>
         </is>
       </c>
@@ -1639,7 +1669,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1806,6 +1836,11 @@
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>INVEGA 9MG EXTENDED- RELEASE TABLETS</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-41E8A50DE3C5</t>
         </is>
       </c>
@@ -1829,7 +1864,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1984,6 +2019,11 @@
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>INFLA-BAN 50MG SUPP.</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-EC12707A831A</t>
         </is>
       </c>
@@ -2007,7 +2047,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2166,6 +2206,11 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>JOINTACE TABLET</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-CEF2722630BB</t>
         </is>
       </c>
@@ -2189,7 +2234,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2356,6 +2401,11 @@
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>KLAVOX SUSPENSION 156MG-5ML</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-98DC5D0A2911</t>
         </is>
       </c>
@@ -2379,7 +2429,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2550,6 +2600,11 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>KLAVOX 625MG F.C.TAB</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-229C52DF6F1F</t>
         </is>
       </c>
@@ -2573,7 +2628,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2736,6 +2791,11 @@
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>KLAVOX 457MG\5ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-A0E254057AB8</t>
         </is>
       </c>
@@ -2759,7 +2819,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2918,6 +2978,11 @@
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>KORANDIL</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-15E363AB1414</t>
         </is>
       </c>
@@ -2941,7 +3006,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3108,6 +3173,11 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>KULAX 65MG-100ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-99842AE393C7</t>
         </is>
       </c>
@@ -3131,7 +3201,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3298,6 +3368,11 @@
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>LACINE 50MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-BFE792BE5134</t>
         </is>
       </c>
@@ -3321,7 +3396,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3488,6 +3563,11 @@
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>KLAVOX 375MG F.C.TAB</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-FE623A9BF70A</t>
         </is>
       </c>
@@ -3511,7 +3591,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3674,6 +3754,11 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>KWELL SHAMPOO</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-091507D153A9</t>
         </is>
       </c>
@@ -3697,7 +3782,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3856,6 +3941,11 @@
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>KWELL LOTION</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-DB144C3C3D47</t>
         </is>
       </c>
@@ -3879,7 +3969,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4042,6 +4132,11 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>KWELL CREAM</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-D8D074C888EA</t>
         </is>
       </c>
@@ -4065,7 +4160,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4232,6 +4327,11 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>KULAX 65MG-100ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-DA02AC94949E</t>
         </is>
       </c>
@@ -4255,7 +4355,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4426,6 +4526,11 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>JOINTACE TABLET</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-540FB2C352D2</t>
         </is>
       </c>
@@ -4449,7 +4554,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4616,6 +4721,11 @@
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>KLAVOX 312.5 MG-5ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-474EE4711158</t>
         </is>
       </c>
@@ -4639,7 +4749,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4802,6 +4912,11 @@
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>KLAVOX 1GM TAB</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-0DD16ED5D028</t>
         </is>
       </c>
@@ -4825,7 +4940,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4996,6 +5111,11 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>KETONIL 1MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-245D2F1CA545</t>
         </is>
       </c>
@@ -5019,7 +5139,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5182,6 +5302,11 @@
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>KETOFAN 25MG TAB</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-681F666CC000</t>
         </is>
       </c>
@@ -5205,7 +5330,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5364,6 +5489,11 @@
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>KETESSE 25MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-71A60C58F75C</t>
         </is>
       </c>
@@ -5387,7 +5517,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5554,6 +5684,11 @@
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>KERASAL 10 % OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-43D1430CD632</t>
         </is>
       </c>
@@ -5577,7 +5712,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5734,6 +5869,11 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>KARVOL DECOGESTANT CAPS</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-B366658CB79F</t>
         </is>
       </c>
@@ -5757,7 +5897,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5924,6 +6064,11 @@
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>KAPECT SUSP.</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-32906AC0FA07</t>
         </is>
       </c>
@@ -5947,7 +6092,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6114,6 +6259,11 @@
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>KAFOSED SYRUP 15MG-5ML</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-DE51B8C020D3</t>
         </is>
       </c>
@@ -6137,7 +6287,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6300,6 +6450,11 @@
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>KLARIMID 500MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-428C240BA10C</t>
         </is>
       </c>
@@ -6323,7 +6478,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6490,6 +6645,11 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>KLARIMID 250MG-5ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-F3E0F10A164E</t>
         </is>
       </c>
@@ -6513,7 +6673,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6676,6 +6836,11 @@
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>KLARIMID 250MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-FF00EE2730CF</t>
         </is>
       </c>
@@ -6699,7 +6864,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6868,6 +7033,11 @@
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>KLACID XL 500MG TAB</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-5417976F18FF</t>
         </is>
       </c>
@@ -6891,7 +7061,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7064,6 +7234,11 @@
       </c>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>KLACID XL 500MG TAB</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-76D9EEE7F95D</t>
         </is>
       </c>
@@ -7087,7 +7262,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7254,6 +7429,11 @@
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>KLAVOX 228MG\5ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-1AE8C8742D0F</t>
         </is>
       </c>
@@ -7277,7 +7457,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7450,6 +7630,11 @@
       </c>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>KLACID 500MG COATED TAB</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-5A82A8DECC54</t>
         </is>
       </c>
@@ -7473,7 +7658,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7646,6 +7831,11 @@
       </c>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>KLACID 250MG TAB</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-D2C132E7C03B</t>
         </is>
       </c>
@@ -7669,7 +7859,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7832,6 +8022,11 @@
       </c>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>INFLABAN 12.5MG SUPP.</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-205105182E79</t>
         </is>
       </c>
@@ -7855,7 +8050,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -8018,6 +8213,11 @@
       </c>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>INFLA-BAN 100MG SUPP.</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-F44B16ECD4CF</t>
         </is>
       </c>
@@ -8041,7 +8241,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8212,6 +8412,11 @@
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>Zistan SYRUP</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-D6BB813C27EA</t>
         </is>
       </c>
@@ -8235,7 +8440,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8406,6 +8611,11 @@
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>Zistan 4 MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-9BAC36EF3F51</t>
         </is>
       </c>
@@ -8429,7 +8639,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8592,6 +8802,11 @@
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>HI-CAL</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-A9BE1E67B2B6</t>
         </is>
       </c>
@@ -8615,7 +8830,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8786,6 +9001,11 @@
       </c>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>HISTOFEN SYRUP 1MG/5ML</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-57A435A00D47</t>
         </is>
       </c>
@@ -8809,7 +9029,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8976,6 +9196,11 @@
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>HISTOP 2MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-8A7C60A29F50</t>
         </is>
       </c>
@@ -8999,7 +9224,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9166,6 +9391,11 @@
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>HI- QUIN 4% CREAM</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-6442EBD79E7B</t>
         </is>
       </c>
@@ -9189,7 +9419,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9356,6 +9586,11 @@
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>HISTOP TAB 4MG</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-B801E6E1E74B</t>
         </is>
       </c>
@@ -9379,7 +9614,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9546,6 +9781,11 @@
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>HUMALOG 100 I.U VIALS</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-7B1F022E743A</t>
         </is>
       </c>
@@ -9569,7 +9809,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9740,6 +9980,11 @@
       </c>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>HI- QUIN 2% CREAM</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-A03A3299F661</t>
         </is>
       </c>
@@ -9763,7 +10008,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9926,6 +10171,11 @@
       </c>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>HARNAL 0.4MG MODIFIED RELEASE CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-6026553F7092</t>
         </is>
       </c>
@@ -9949,7 +10199,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10120,6 +10370,11 @@
       </c>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>HALDOL 5MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-EFB3E131F464</t>
         </is>
       </c>
@@ -10143,7 +10398,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10306,6 +10561,11 @@
       </c>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>HALDOL 2MG-ML DROPS</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-34F1BF7B7D78</t>
         </is>
       </c>
@@ -10329,7 +10589,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10488,6 +10748,11 @@
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>HAIRGROW</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-C7A55C7117B6</t>
         </is>
       </c>
@@ -10511,7 +10776,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10670,6 +10935,11 @@
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>HAIRGROW</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-BD01D11859EF</t>
         </is>
       </c>
@@ -10693,7 +10963,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10856,6 +11126,11 @@
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>HAIRGAIN 5% W-V SOLUTION FOR MEN</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-A3E611EB6C64</t>
         </is>
       </c>
@@ -10879,7 +11154,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -11042,6 +11317,11 @@
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>HAIRGAIN 2% W-V SOLUTION FOR WOMEN</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-4E5A4C55F092</t>
         </is>
       </c>
@@ -11065,7 +11345,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11236,6 +11516,11 @@
       </c>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>HEMAMAX 100 MG CHEWABLE OR SWALLOWABLE TABLETS</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-F97AEC5B5432</t>
         </is>
       </c>
@@ -11259,7 +11544,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11422,6 +11707,11 @@
       </c>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>HEMAMAX 50 MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-6768671BA798</t>
         </is>
       </c>
@@ -11445,7 +11735,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11612,6 +11902,11 @@
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>HEMAMAX F CHEWABLE TABLETS</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-0A305E09F332</t>
         </is>
       </c>
@@ -11635,7 +11930,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11798,6 +12093,11 @@
       </c>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>HEMOCLAR CREAM 0.5GM-100GM</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-B1114124F21B</t>
         </is>
       </c>
@@ -11821,7 +12121,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11980,6 +12280,11 @@
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>HEPIX 100MG F-C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-F16ADC1D999C</t>
         </is>
       </c>
@@ -12003,7 +12308,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12166,6 +12471,11 @@
       </c>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>HI CARE CREAM</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-F2BE2823797C</t>
         </is>
       </c>
@@ -12189,7 +12499,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12352,6 +12662,11 @@
       </c>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>Hepa-Merz</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-634D739D5C1E</t>
         </is>
       </c>
@@ -12375,7 +12690,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12538,6 +12853,11 @@
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>IMODIUM 2MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-DDF1F875AB3A</t>
         </is>
       </c>
@@ -12561,7 +12881,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12732,6 +13052,11 @@
       </c>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>IMIGRAN</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-FB843B61CAD9</t>
         </is>
       </c>
@@ -12755,7 +13080,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12932,6 +13257,11 @@
       </c>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>INFANRIX HEXA VACCINE</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-A61275FF3A17</t>
         </is>
       </c>
@@ -12955,7 +13285,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13118,6 +13448,11 @@
       </c>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>INDOMIN CAP 25MG</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-F9C978A09BF1</t>
         </is>
       </c>
@@ -13141,7 +13476,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13304,6 +13639,11 @@
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>IMIGRAN</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-62571E271ECB</t>
         </is>
       </c>
@@ -13327,7 +13667,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13486,6 +13826,11 @@
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>INDOMETHACIN CAPS 25MG</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-60342377A10B</t>
         </is>
       </c>
@@ -13509,7 +13854,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13680,6 +14025,11 @@
       </c>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>INDICARDIN 10 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-CBFCC63AC0E3</t>
         </is>
       </c>
@@ -13703,7 +14053,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13874,6 +14224,11 @@
       </c>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>INDICARDIN 40 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-AEBA2CD86504</t>
         </is>
       </c>
@@ -13897,7 +14252,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -14064,6 +14419,11 @@
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>INDERAL TABLETS 40 MG.</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-B6D84291CDB7</t>
         </is>
       </c>
@@ -14087,7 +14447,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14254,6 +14614,11 @@
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>INDERAL TABLETS 10 MG.</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-ED176421E201</t>
         </is>
       </c>
@@ -14277,7 +14642,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14444,6 +14809,11 @@
       </c>
       <c r="AT74" t="inlineStr">
         <is>
+          <t xml:space="preserve">VERORAB VACCINE </t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-2E6871F31C93</t>
         </is>
       </c>
@@ -14467,7 +14837,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14634,6 +15004,11 @@
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>INDOCID 100MG SUPPOSITORIES</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-3293E6A7FD2B</t>
         </is>
       </c>
@@ -14657,7 +15032,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14828,6 +15203,11 @@
       </c>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>IMIGRAN</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-67C18EB758DB</t>
         </is>
       </c>
@@ -14851,7 +15231,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -15024,6 +15404,11 @@
       </c>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>IMIGRAN</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-0658EBAC2150</t>
         </is>
       </c>
@@ -15047,7 +15432,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15210,6 +15595,11 @@
       </c>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>IMAVIR 5% CREAM</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-D788197876A7</t>
         </is>
       </c>
@@ -15233,7 +15623,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15404,6 +15794,11 @@
       </c>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>HYMOX 125MG-5ML POWDER FOR ORAL SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-E2647B87F634</t>
         </is>
       </c>
@@ -15427,7 +15822,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15594,6 +15989,11 @@
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>HYLO-COMOD 0.1% EYE DROP</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-B521548008DF</t>
         </is>
       </c>
@@ -15617,7 +16017,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15788,6 +16188,11 @@
       </c>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>HYFRESH 2 MG- ML OPHTHALMIC SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-5A217C0516FE</t>
         </is>
       </c>
@@ -15811,7 +16216,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15974,6 +16379,11 @@
       </c>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>HYDROSONE 20MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-E7EFF600ADBB</t>
         </is>
       </c>
@@ -15997,7 +16407,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16168,6 +16578,11 @@
       </c>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>HYMOX 250MG CAPS</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-36D054AC652B</t>
         </is>
       </c>
@@ -16191,7 +16606,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16370,6 +16785,11 @@
       </c>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>HUMULIN-R-REGULAR 100 U-ML</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-9C1D5A6920B0</t>
         </is>
       </c>
@@ -16393,7 +16813,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16568,6 +16988,11 @@
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>HUMULIN-N-NPH 100 U-ML</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-D2D5DFF34515</t>
         </is>
       </c>
@@ -16591,7 +17016,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16766,6 +17191,11 @@
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>HUMULIN 70-30 100U-ML</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-B458DB445835</t>
         </is>
       </c>
@@ -16789,7 +17219,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16948,6 +17378,11 @@
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>HYDRODERM CREAM PLUS</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-31A03C64D0AB</t>
         </is>
       </c>
@@ -16971,7 +17406,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -17130,6 +17565,11 @@
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>FLUZYN 20MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-D1CA808A4451</t>
         </is>
       </c>
@@ -17153,7 +17593,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17316,6 +17756,11 @@
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>HYMOX 250MG-5ML POWDER FOR ORAL SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-BC54AB22F92C</t>
         </is>
       </c>
@@ -17339,7 +17784,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17510,6 +17955,11 @@
       </c>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>HYMOX 500MG CAPS</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-BF028241B2A1</t>
         </is>
       </c>
@@ -17533,7 +17983,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17688,6 +18138,11 @@
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>IMAVIR 5% CREAM</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-B537FFB3F6D8</t>
         </is>
       </c>
@@ -17711,7 +18166,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17874,6 +18329,11 @@
       </c>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>ICHTHAMMOL 10% OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-547A1130D957</t>
         </is>
       </c>
@@ -17897,7 +18357,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -18060,6 +18520,11 @@
       </c>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>IBUTOP 5% GEL</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-C8202798F0CA</t>
         </is>
       </c>
@@ -18083,7 +18548,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18242,6 +18707,11 @@
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>IBUTOP</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-D61C54F90485</t>
         </is>
       </c>
@@ -18265,7 +18735,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18428,6 +18898,11 @@
       </c>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>Brofenex 5GM- 100GM CREAM</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-F027C6351E0E</t>
         </is>
       </c>
@@ -18451,7 +18926,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18624,6 +19099,11 @@
       </c>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>HYZAAR 50/12.5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-5D8AF580306C</t>
         </is>
       </c>
@@ -18647,7 +19127,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18818,6 +19298,11 @@
       </c>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>HYPOSEC 20 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-C86D6493E921</t>
         </is>
       </c>
@@ -18841,7 +19326,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -19004,6 +19489,11 @@
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>HYPODIPINE 5MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-BB388FCC1729</t>
         </is>
       </c>
@@ -19027,7 +19517,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19198,6 +19688,11 @@
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>HYOPAN SYRUP 5 MG-5 ML</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-FF773A185556</t>
         </is>
       </c>
@@ -19221,7 +19716,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19388,6 +19883,11 @@
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>HYMOX 875 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-EB3C1F372648</t>
         </is>
       </c>
@@ -19411,7 +19911,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19569,6 +20069,11 @@
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>HYZAAR</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-A584401C11BF</t>
         </is>
@@ -19585,7 +20090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19631,100 +20136,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19756,7 +20266,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19771,92 +20281,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-29540</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>315.12</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>131</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19888,7 +20403,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19903,92 +20418,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-56441</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>192.94</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>132</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20020,7 +20540,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -20035,92 +20555,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-65215</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>368.87</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>133</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20152,7 +20677,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20167,92 +20692,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-52557</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>83.77</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>134</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20284,7 +20814,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20299,92 +20829,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-49315</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>150.56</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>135</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20416,7 +20951,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20431,92 +20966,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-13231</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>153.56</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>136</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20548,7 +21088,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20563,92 +21103,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-50272</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>191.56</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>137</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20680,7 +21225,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20695,92 +21240,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-95338</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>123.79</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>138</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20812,7 +21362,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20827,92 +21377,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-40957</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>303.07</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>139</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20944,7 +21499,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20959,92 +21514,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-60878</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>328.33</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>140</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21076,7 +21636,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -21091,92 +21651,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-26339</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>191.41</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>141</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21193,7 +21758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21299,6 +21864,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21334,7 +21909,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21399,6 +21974,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-A511C2468565</t>
         </is>
@@ -21435,7 +22020,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21500,6 +22085,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-1641753454D0</t>
         </is>
@@ -21536,7 +22131,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21601,6 +22196,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-D2079A90D2DD</t>
         </is>
@@ -21637,7 +22242,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21702,6 +22307,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-0CE7B7D61714</t>
         </is>
@@ -21738,7 +22353,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21803,6 +22418,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-A9CF43D9BBD3</t>
         </is>
@@ -21839,7 +22464,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21904,6 +22529,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-AB47B8A03FBF</t>
         </is>
@@ -21940,7 +22575,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -22005,6 +22640,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-FA5C343DCC0A</t>
         </is>
@@ -22041,7 +22686,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -22106,6 +22751,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-A31D463D5DC4</t>
         </is>
@@ -22142,7 +22797,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22207,6 +22862,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-C2F133C28E99</t>
         </is>
@@ -22243,7 +22908,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22308,6 +22973,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-37FECC61EABB</t>
         </is>
@@ -22344,7 +23019,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22409,6 +23084,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-6A1B7BE9B1E2</t>
         </is>
@@ -22445,7 +23130,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22510,6 +23195,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-E1D659E2C9E2</t>
         </is>
@@ -22546,7 +23241,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22611,6 +23306,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-96A06D975682</t>
         </is>
@@ -22647,7 +23352,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22712,6 +23417,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-1F99A562DB00</t>
         </is>
@@ -22748,7 +23463,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22813,6 +23528,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-A185806722B0</t>
         </is>
@@ -22849,7 +23574,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22914,6 +23639,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-E3CE5C30AC0D</t>
         </is>
@@ -22950,7 +23685,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -23015,6 +23750,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-1B40CE4DB751</t>
         </is>
@@ -23051,7 +23796,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -23116,6 +23861,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-BE0DC435B170</t>
         </is>
@@ -23152,7 +23907,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23217,6 +23972,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-E2355880AC64</t>
         </is>
@@ -23253,7 +24018,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23318,6 +24083,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-2044734CD08B</t>
         </is>

--- a/product_upload/packages/21/file.xlsx
+++ b/product_upload/packages/21/file.xlsx
@@ -1872,8 +1872,16 @@
           <t>2492297437-113-597248545964</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ INFLA-BAN 50MG SUPP.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>INFLA-BAN 50MG SUPP. detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -2055,8 +2063,16 @@
           <t>9005053125-539-171927653780</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ JOINTACE TABLET</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>JOINTACE TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
@@ -2827,8 +2843,16 @@
           <t>0637842997-395-554782902224</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ KORANDIL</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>KORANDIL detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
@@ -3014,8 +3038,16 @@
           <t>4503874599-708-305984319090</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ KULAX 65MG-100ML SYRUP</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>KULAX 65MG-100ML SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
@@ -3599,8 +3631,16 @@
           <t>9607806535-439-791016092429</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ KWELL SHAMPOO</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>KWELL SHAMPOO detailed description.</t>
+        </is>
+      </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
@@ -3790,8 +3830,16 @@
           <t>7014933044-568-051567564738</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ KWELL LOTION</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>KWELL LOTION detailed description.</t>
+        </is>
+      </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
@@ -3977,8 +4025,16 @@
           <t>1102786274-748-421365329026</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ KWELL CREAM</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>KWELL CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
@@ -4168,8 +4224,16 @@
           <t>6664193525-656-051275304115</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ KULAX 65MG-100ML SYRUP</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>KULAX 65MG-100ML SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
@@ -5338,8 +5402,16 @@
           <t>8894664736-345-946801850403</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ KETESSE 25MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>KETESSE 25MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
@@ -5720,8 +5792,16 @@
           <t>9552028490-002-117181405676</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ KARVOL DECOGESTANT CAPS</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>KARVOL DECOGESTANT CAPS detailed description.</t>
+        </is>
+      </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
@@ -6295,8 +6375,16 @@
           <t>6641311967-399-729612301851</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ KLARIMID 500MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>KLARIMID 500MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
@@ -6486,8 +6574,16 @@
           <t>8453916111-532-389284652695</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ KLARIMID 250MG-5ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>KLARIMID 250MG-5ML SUSPENSION detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
@@ -6681,8 +6777,16 @@
           <t>9432341986-803-885722333531</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ KLARIMID 250MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>KLARIMID 250MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
@@ -7867,8 +7971,16 @@
           <t>3209786245-932-419395575626</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ INFLABAN 12.5MG SUPP.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>INFLABAN 12.5MG SUPP. detailed description.</t>
+        </is>
+      </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
@@ -8058,8 +8170,16 @@
           <t>2326227726-957-296075847605</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ INFLA-BAN 100MG SUPP.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>INFLA-BAN 100MG SUPP. detailed description.</t>
+        </is>
+      </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
@@ -8647,8 +8767,16 @@
           <t>0352844348-329-761538893096</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HI-CAL</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>HI-CAL detailed description.</t>
+        </is>
+      </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
@@ -9622,8 +9750,16 @@
           <t>4208739284-001-355023263222</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HUMALOG 100 I.U VIALS</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>HUMALOG 100 I.U VIALS detailed description.</t>
+        </is>
+      </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
@@ -10016,8 +10152,16 @@
           <t>4533579290-230-830718923882</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HARNAL 0.4MG MODIFIED RELEASE CAPSULES</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>HARNAL 0.4MG MODIFIED RELEASE CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
@@ -10406,8 +10550,16 @@
           <t>6929551224-600-480263390627</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HALDOL 2MG-ML DROPS</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>HALDOL 2MG-ML DROPS detailed description.</t>
+        </is>
+      </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
@@ -10597,8 +10749,16 @@
           <t>7802441229-506-791671021658</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HAIRGROW</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>HAIRGROW detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
@@ -10784,8 +10944,16 @@
           <t>7119863039-287-909908772611</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HAIRGROW</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>HAIRGROW detailed description.</t>
+        </is>
+      </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
@@ -10971,8 +11139,16 @@
           <t>8494289929-015-001479424104</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HAIRGAIN 5% W-V SOLUTION FOR MEN</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>HAIRGAIN 5% W-V SOLUTION FOR MEN detailed description.</t>
+        </is>
+      </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
@@ -11162,8 +11338,16 @@
           <t>8583299231-966-728326580911</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HAIRGAIN 2% W-V SOLUTION FOR WOMEN</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>HAIRGAIN 2% W-V SOLUTION FOR WOMEN detailed description.</t>
+        </is>
+      </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
@@ -11552,8 +11736,16 @@
           <t>9223961575-477-947963943709</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HEMAMAX 50 MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>HEMAMAX 50 MG-5ML SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
@@ -11938,8 +12130,16 @@
           <t>3052080312-084-590206192208</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HEMOCLAR CREAM 0.5GM-100GM</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>HEMOCLAR CREAM 0.5GM-100GM detailed description.</t>
+        </is>
+      </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
@@ -12129,8 +12329,16 @@
           <t>4767598026-560-051290987736</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HEPIX 100MG F-C TABLETS</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>HEPIX 100MG F-C TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -12316,8 +12524,16 @@
           <t>5139257192-311-492496241581</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HI CARE CREAM</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>HI CARE CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
@@ -12507,8 +12723,16 @@
           <t>0366995541-230-755741653003</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Hepa-Merz</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Hepa-Merz detailed description.</t>
+        </is>
+      </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
@@ -13293,8 +13517,16 @@
           <t>2665340268-678-437883566699</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ INDOMIN CAP 25MG</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>INDOMIN CAP 25MG detailed description.</t>
+        </is>
+      </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
@@ -13675,8 +13907,16 @@
           <t>3290886427-068-853716582231</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ INDOMETHACIN CAPS 25MG</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>INDOMETHACIN CAPS 25MG detailed description.</t>
+        </is>
+      </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
@@ -14650,8 +14890,16 @@
           <t>0924622699-115-515243500561</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VERORAB VACCINE</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>VERORAB VACCINE detailed description.</t>
+        </is>
+      </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
@@ -15440,8 +15688,16 @@
           <t>8486682757-184-012812829494</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ IMAVIR 5% CREAM</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>IMAVIR 5% CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
@@ -16224,8 +16480,16 @@
           <t>2577557550-482-955159996224</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HYDROSONE 20MG TABLET</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>HYDROSONE 20MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
@@ -17227,8 +17491,16 @@
           <t>9470854641-929-311424046264</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HYDRODERM CREAM PLUS</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>HYDRODERM CREAM PLUS detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -17414,8 +17686,16 @@
           <t>8961721767-510-365849585984</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FLUZYN 20MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>FLUZYN 20MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -17991,8 +18271,16 @@
           <t>0050308275-114-683406536306</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ IMAVIR 5% CREAM</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>IMAVIR 5% CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
@@ -18174,8 +18462,16 @@
           <t>5951366167-984-587136969884</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ICHTHAMMOL 10% OINTMENT</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>ICHTHAMMOL 10% OINTMENT detailed description.</t>
+        </is>
+      </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
@@ -18365,8 +18661,16 @@
           <t>0429728013-168-027626746138</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ IBUTOP 5% GEL</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>IBUTOP 5% GEL detailed description.</t>
+        </is>
+      </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
@@ -18556,8 +18860,16 @@
           <t>9398928219-816-171408406981</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ IBUTOP</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>IBUTOP detailed description.</t>
+        </is>
+      </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
@@ -18743,8 +19055,16 @@
           <t>8818702279-416-235586710493</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Brofenex 5GM- 100GM CREAM</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Brofenex 5GM- 100GM CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
@@ -19334,8 +19654,16 @@
           <t>5132295340-163-981453680854</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HYPODIPINE 5MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>HYPODIPINE 5MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
@@ -19919,8 +20247,16 @@
           <t>0159640183-769-260453766552</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HYZAAR</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>HYZAAR detailed description.</t>
+        </is>
+      </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/21/file.xlsx
+++ b/product_upload/packages/21/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20472,7 +20472,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22094,7 +22094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22175,40 +22175,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22288,38 +22293,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>53.88</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-A511C2468565</t>
         </is>
@@ -22399,38 +22409,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>479.27</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-1641753454D0</t>
         </is>
@@ -22510,38 +22525,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>159.38</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-D2079A90D2DD</t>
         </is>
@@ -22621,38 +22641,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>349.3</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-0CE7B7D61714</t>
         </is>
@@ -22732,38 +22757,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>204.84</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-A9CF43D9BBD3</t>
         </is>
@@ -22843,38 +22873,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>208.12</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-AB47B8A03FBF</t>
         </is>
@@ -22954,38 +22989,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>196.03</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-FA5C343DCC0A</t>
         </is>
@@ -23065,38 +23105,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>208.08</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-A31D463D5DC4</t>
         </is>
@@ -23176,38 +23221,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>227.45</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-C2F133C28E99</t>
         </is>
@@ -23287,38 +23337,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>26.84</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-37FECC61EABB</t>
         </is>
@@ -23398,38 +23453,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>260.53</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-6A1B7BE9B1E2</t>
         </is>
@@ -23509,38 +23569,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>356.46</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-E1D659E2C9E2</t>
         </is>
@@ -23620,38 +23685,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>114.03</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-96A06D975682</t>
         </is>
@@ -23731,38 +23801,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>112.67</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-1F99A562DB00</t>
         </is>
@@ -23842,38 +23917,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>100.45</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-A185806722B0</t>
         </is>
@@ -23953,38 +24033,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>300.17</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-E3CE5C30AC0D</t>
         </is>
@@ -24064,38 +24149,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>133.18</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-1B40CE4DB751</t>
         </is>
@@ -24175,38 +24265,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>362.7</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-BE0DC435B170</t>
         </is>
@@ -24286,38 +24381,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>383.26</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-E2355880AC64</t>
         </is>
@@ -24397,38 +24497,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>183.31</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-2044734CD08B</t>
         </is>
